--- a/waiver_forms/018_waxing_waiver_form--waiver_forms.xlsx
+++ b/waiver_forms/018_waxing_waiver_form--waiver_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>emergency_contact_phone</t>
+          <t>emergency_contact_phone_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Emergency Contact Phone</t>
+          <t>Emergency Contact Phone 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>emergency_contact_relationship</t>
+          <t>emergency_contact_relationship_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Emergency Contact Relationship</t>
+          <t>Emergency Contact Relationship 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>emergency_contact_address</t>
+          <t>emergency_contact_address_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Emergency Contact Address</t>
+          <t>Emergency Contact Address 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -872,8 +872,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'allergies',_'label':_'allergies'}</t>
+          <t>allergies</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Allergies', 'label': 'Allergies'}</t>
+          <t>Allergies</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'medication',_'label':_'medication'}</t>
+          <t>medication</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Medication', 'label': 'Medication'}</t>
+          <t>Medication</t>
         </is>
       </c>
     </row>
